--- a/rules/CORE-000191/negative/01/data/unit-test-coreid-CG0529-negative.xlsx
+++ b/rules/CORE-000191/negative/01/data/unit-test-coreid-CG0529-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulieChason\GitHub\core-contributor\rules\CORE-000191\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24994436-38F9-4F52-9126-F3166CB8EFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8295E241-111B-4859-857F-D1E2AB749BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>Product</t>
   </si>
@@ -180,7 +180,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,6 +191,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -221,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -235,6 +241,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -590,7 +599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.4">
@@ -626,10 +635,29 @@
       <c r="D2" s="5">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="5">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -761,11 +789,11 @@
       <c r="E5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="6"/>
       <c r="G5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="6" t="s">
         <v>37</v>
       </c>
     </row>
